--- a/output/xlsx/AdministradorDeletaAdministrador--GT-.xlsx
+++ b/output/xlsx/AdministradorDeletaAdministrador--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="66">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 4 test case(s)</t>
+    <t>Size: 8 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -122,13 +122,13 @@
     <t>Administrador: confirma delecao</t>
   </si>
   <si>
-    <t>SYSTEM notifica que o Administrador foi excluido com sucesso</t>
+    <t>SYSTEM notifica que o Administrador foi adicionado com sucesso</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
   </si>
   <si>
-    <t>O Administrador foi excluido com sucesso.</t>
+    <t>O Administrador foi adicionado com sucesso.</t>
   </si>
   <si>
     <t>TC2</t>
@@ -146,7 +146,7 @@
     <t>Alternative Flow 2: Cancela delecao de Administrador</t>
   </si>
   <si>
-    <t>Administrador: clica no botao 'Cancelar'</t>
+    <t>Administrador: clica no botao Cancelar</t>
   </si>
   <si>
     <t>TC4</t>
@@ -156,6 +156,60 @@
   </si>
   <si>
     <t>Administrador: clica no botao 'Cancelar' do popup</t>
+  </si>
+  <si>
+    <t>TC5</t>
+  </si>
+  <si>
+    <t>Exception Flow 1: Dados obrigatorios'</t>
+  </si>
+  <si>
+    <t>SYSTEM informa que os dados obrigatorios devem ser preenchidos</t>
+  </si>
+  <si>
+    <t>Administrador: preenche os dados orbigatorios e clica no botao 'Registrar'</t>
+  </si>
+  <si>
+    <t>SYSTEM processes action successfully</t>
+  </si>
+  <si>
+    <t>Flow interrupted due to exception / error</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
+    <t>Exception Flow 2: Email invalido</t>
+  </si>
+  <si>
+    <t>SYSTEM alerta usuario de que Email e invalido</t>
+  </si>
+  <si>
+    <t>Administrador: insere um Email valido e clica no botao 'Registrar'</t>
+  </si>
+  <si>
+    <t>TC7</t>
+  </si>
+  <si>
+    <t>Exception Flow 3: Senha e Confirmacao diferentes</t>
+  </si>
+  <si>
+    <t>SYSTEM alerta usuario de que senhas estao diferentes</t>
+  </si>
+  <si>
+    <t>Administrador: insere Senhas iguais e clica no botao 'Registrar'</t>
+  </si>
+  <si>
+    <t>TC8</t>
+  </si>
+  <si>
+    <t>Exception Flow 4: Sem Permissao</t>
+  </si>
+  <si>
+    <t>SYSTEM alerta usuario que Administrador nao esta com nenhuma Permissao</t>
+  </si>
+  <si>
+    <t>Administrador: insere uma permissao e clica no botao 'Registrar'</t>
   </si>
 </sst>
 </file>
@@ -247,11 +301,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="58.4609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="60.32421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="63.30078125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
@@ -1061,6 +1115,730 @@
         <v>38</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C60" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E61" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B64" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B65" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D65" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E65" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F65" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B66" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C66" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D66" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E66" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F66" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B67" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C67" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D67" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E67" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F67" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B68" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C68" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D68" t="s" s="3">
+        <v>50</v>
+      </c>
+      <c r="E68" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F68" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B69" t="s" s="3">
+        <v>51</v>
+      </c>
+      <c r="C69" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D69" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E69" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F69" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C73" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="E74" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B77" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F77" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B78" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E78" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F78" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B79" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C79" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D79" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E79" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F79" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B80" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C80" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E80" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F80" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B81" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C81" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D81" t="s" s="3">
+        <v>56</v>
+      </c>
+      <c r="E81" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F81" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B82" t="s" s="3">
+        <v>57</v>
+      </c>
+      <c r="C82" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D82" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E82" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F82" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C86" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E87" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D89" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B90" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D90" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E90" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F90" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B91" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C91" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D91" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E91" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F91" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B92" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C92" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D92" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E92" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F92" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B93" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C93" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D93" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E93" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F93" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B94" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C94" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D94" t="s" s="3">
+        <v>60</v>
+      </c>
+      <c r="E94" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F94" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B95" t="s" s="3">
+        <v>61</v>
+      </c>
+      <c r="C95" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D95" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E95" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F95" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C99" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="E100" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B103" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D103" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E103" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F103" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B104" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C104" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D104" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E104" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F104" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B105" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C105" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D105" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E105" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F105" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B106" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C106" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D106" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E106" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F106" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B107" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C107" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D107" t="s" s="3">
+        <v>64</v>
+      </c>
+      <c r="E107" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F107" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B108" t="s" s="3">
+        <v>65</v>
+      </c>
+      <c r="C108" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D108" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E108" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F108" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
